--- a/docs/規格來源/第二階段-賠款月帳單/產出範例/當月賠款月帳單-T字帳113範例.xlsx
+++ b/docs/規格來源/第二階段-賠款月帳單/產出範例/當月賠款月帳單-T字帳113範例.xlsx
@@ -3,21 +3,21 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/檔案位子範例/產出範例/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64cd5bb3604bb353/Desktop/共保志工險/規格書/檔案位子範例/templet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA2A67E-3C80-415B-A312-ED0703D50045}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_AD4DBB64A54DDB1B405E389605D904C94E90DF19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{563BB598-8752-44BB-B628-5EE88C7E236E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-8370" windowWidth="16440" windowHeight="28320" tabRatio="577" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="共保賠款月帳單-T字帳" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>執行災害防救業務志工團體保險共保組織</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,13 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>115 年</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 05 月</t>
-  </si>
-  <si>
     <t>To: 共保系統</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -75,24 +68,27 @@
     <t>授權簽署</t>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>U/Y:2024</t>
+    <t>U/Y:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>共保賠款月帳單</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115 年 05 月</t>
+  </si>
+  <si>
+    <t>2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -148,11 +144,12 @@
       <charset val="136"/>
     </font>
     <font>
-      <u val="double"/>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -164,7 +161,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -263,12 +260,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -292,6 +298,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -305,6 +313,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -321,10 +331,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,69 +599,69 @@
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.0"/>
+    <col min="2" max="2" customWidth="true" width="3.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="10" max="10" customWidth="true" width="3.42578125"/>
+    <col min="13" max="13" customWidth="true" width="10.85546875"/>
+    <col min="15" max="15" customWidth="true" width="10.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="27.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
       <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
+      <c r="A2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
       <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>3</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -665,7 +671,7 @@
     </row>
     <row r="4" spans="1:16" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -681,14 +687,16 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
+      <c r="B5" s="14" t="s">
+        <v>3</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -697,8 +705,8 @@
       <c r="G5" s="4"/>
       <c r="H5" s="5"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
+      <c r="J5" s="14" t="s">
+        <v>4</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -709,18 +717,18 @@
     </row>
     <row r="6" spans="1:16" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>32460</v>
+      <c r="C6" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n" s="20">
+        <v>32460.0</v>
       </c>
       <c r="H6" s="8"/>
       <c r="K6" t="s">
-        <v>7</v>
-      </c>
-      <c r="O6" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="O6" t="n" s="20">
+        <v>0.0</v>
       </c>
       <c r="P6" s="8"/>
     </row>
@@ -754,18 +762,18 @@
       <c r="H12" s="8"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" t="s">
-        <v>8</v>
+      <c r="B13" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="H13" s="8"/>
       <c r="P13" s="8"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="G14" t="s">
-        <v>11</v>
+      <c r="G14" t="n" s="20">
+        <v>0.0</v>
       </c>
       <c r="H14" s="8"/>
       <c r="P14" s="8"/>
@@ -798,26 +806,26 @@
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="H20" s="8"/>
-      <c r="O20">
-        <v>32460</v>
+      <c r="O20" t="n" s="20">
+        <v>32460.0</v>
       </c>
       <c r="P20" s="8"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-      <c r="G21">
-        <v>32460</v>
+      <c r="B21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n" s="20">
+        <v>32460.0</v>
       </c>
       <c r="H21" s="8"/>
-      <c r="O21" s="13">
-        <v>32460</v>
+      <c r="O21" s="21" t="n">
+        <v>32460.0</v>
       </c>
       <c r="P21" s="8"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="H22" s="8"/>
       <c r="P22" s="8"/>
@@ -851,10 +859,10 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="12"/>
-      <c r="N26" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="O26" s="17"/>
+      <c r="N26" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="19"/>
       <c r="P26" s="11"/>
     </row>
   </sheetData>
